--- a/survey_templates/030_sports_prediction_app_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/030_sports_prediction_app_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>How likely are you to recommend us?</t>
+          <t>Select One 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Additional comments</t>
+          <t>Note 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1199,29 +1199,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one_1_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1284,148 +1284,250 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple_1_choices</t>
+          <t>select_one_1_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple_1_choices</t>
+          <t>select_one_1_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple_2_choices</t>
+          <t>select_multiple_1_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple_2_choices</t>
+          <t>select_multiple_1_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one_2_choices</t>
+          <t>select_multiple_1_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one_2_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple_3_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>select_multiple_2_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>select_one_2_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>select_one_2_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>select_one_2_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>select_multiple_3_choices</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Option 2</t>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>select_multiple_3_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>select_multiple_3_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
